--- a/Assets/@Resources/Data/Excel/EquipmentData.xlsx
+++ b/Assets/@Resources/Data/Excel/EquipmentData.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>여행자의 검</t>
+          <t>Equip30001NameText</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">

--- a/Assets/@Resources/Data/Excel/EquipmentData.xlsx
+++ b/Assets/@Resources/Data/Excel/EquipmentData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,16 +582,2199 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>110</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>30002</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Equip30002NameText</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Helmet</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>helmet_01</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>110</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>30003</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Equip30003NameText</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Torso 32 (17)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>110</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>30004</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Equip30004NameText</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Vambrace 32 (52)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>110</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>30005</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Equip30005NameText</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Legs</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Grieves 32 (9)</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>110</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>30006</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Equip30006NameText</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Accessories 32 (1)</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>110</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>30007</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Equip30007NameText</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sword03</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>120</v>
+      </c>
+      <c r="G10" t="n">
+        <v>28</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30008</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Equip30008NameText</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Helmet</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Helmet 32 (27)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>120</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>30009</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Equip30009NameText</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Torso 32 (27)</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>120</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>30010</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Equip30010NameText</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Vambrace 32 (52)</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>120</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>30011</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Equip30011NameText</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Legs</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Grieves 32 (9)</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>120</v>
+      </c>
+      <c r="G14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>30012</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Equip30012NameText</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Cloak 32 (16)</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>120</v>
+      </c>
+      <c r="G15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>30013</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Equip30013NameText</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sword 02</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>130</v>
+      </c>
+      <c r="G16" t="n">
+        <v>47</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>30014</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Equip30014NameText</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Helmet</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>helmet_01</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>130</v>
+      </c>
+      <c r="G17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>30015</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Equip30015NameText</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Torso 32 (17)</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>130</v>
+      </c>
+      <c r="G18" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>30016</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Equip30016NameText</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Vambrace 32 (52)</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>130</v>
+      </c>
+      <c r="G19" t="n">
+        <v>16</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>30017</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Equip30017NameText</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Legs</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Grieves 32 (9)</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>130</v>
+      </c>
+      <c r="G20" t="n">
+        <v>16</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>30018</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Equip30018NameText</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Accessories 32 (1)</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>130</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30019</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Equip30019NameText</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Icon_Sword_2</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>140</v>
+      </c>
+      <c r="G22" t="n">
+        <v>73</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>30020</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Equip30020NameText</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Helmet</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Helmet 32 (27)</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>140</v>
+      </c>
+      <c r="G23" t="n">
+        <v>21</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>30021</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Equip30021NameText</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Torso 32 (27)</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>140</v>
+      </c>
+      <c r="G24" t="n">
+        <v>31</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>30022</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Equip30022NameText</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Vambrace 32 (52)</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>140</v>
+      </c>
+      <c r="G25" t="n">
+        <v>25</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>30023</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Equip30023NameText</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Legs</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Grieves 32 (9)</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>140</v>
+      </c>
+      <c r="G26" t="n">
+        <v>25</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>30024</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Equip30024NameText</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Abnormal</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Cloak 32 (16)</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>140</v>
+      </c>
+      <c r="G27" t="n">
+        <v>33</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>30025</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Equip30025NameText</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sword 32 (5)</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>150</v>
+      </c>
+      <c r="G28" t="n">
+        <v>102</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>30026</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Equip30026NameText</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Helmet</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>helmet_01</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>150</v>
+      </c>
+      <c r="G29" t="n">
+        <v>29</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>30027</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Equip30027NameText</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Torso 32 (17)</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>150</v>
+      </c>
+      <c r="G30" t="n">
+        <v>44</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30028</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Equip30028NameText</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Vambrace 32 (52)</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>150</v>
+      </c>
+      <c r="G31" t="n">
+        <v>35</v>
+      </c>
+      <c r="H31" t="n">
+        <v>5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30029</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Equip30029NameText</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Legs</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Grieves 32 (9)</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>150</v>
+      </c>
+      <c r="G32" t="n">
+        <v>35</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>30030</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Equip30030NameText</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Accessories 32 (1)</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>150</v>
+      </c>
+      <c r="G33" t="n">
+        <v>47</v>
+      </c>
+      <c r="H33" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>30031</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Equip30031NameText</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sword01</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>160</v>
+      </c>
+      <c r="G34" t="n">
+        <v>131</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30032</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Equip30032NameText</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Helmet</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Helmet 32 (27)</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>160</v>
+      </c>
+      <c r="G35" t="n">
+        <v>38</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Equip30033NameText</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Torso 32 (27)</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>160</v>
+      </c>
+      <c r="G36" t="n">
+        <v>56</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>30034</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Equip30034NameText</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Vambrace 32 (52)</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>160</v>
+      </c>
+      <c r="G37" t="n">
+        <v>45</v>
+      </c>
+      <c r="H37" t="n">
+        <v>6</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>30035</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Equip30035NameText</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Legs</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Grieves 32 (9)</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>160</v>
+      </c>
+      <c r="G38" t="n">
+        <v>45</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>30036</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Equip30036NameText</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Cloak 32 (16)</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>160</v>
+      </c>
+      <c r="G39" t="n">
+        <v>60</v>
+      </c>
+      <c r="H39" t="n">
+        <v>9</v>
+      </c>
+      <c r="I39" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>30037</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Equip30037NameText</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Exceptional</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Sword03</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>170</v>
+      </c>
+      <c r="G40" t="n">
+        <v>179</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>30038</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Equip30038NameText</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Helmet</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Exceptional</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>helmet_01</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>170</v>
+      </c>
+      <c r="G41" t="n">
+        <v>51</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>30039</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Equip30039NameText</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Exceptional</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Torso 32 (17)</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>170</v>
+      </c>
+      <c r="G42" t="n">
+        <v>77</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30040</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Equip30040NameText</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Exceptional</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Vambrace 32 (52)</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>170</v>
+      </c>
+      <c r="G43" t="n">
+        <v>61</v>
+      </c>
+      <c r="H43" t="n">
+        <v>7</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>30041</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Equip30041NameText</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Legs</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Exceptional</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Grieves 32 (9)</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>170</v>
+      </c>
+      <c r="G44" t="n">
+        <v>61</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>30042</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Equip30042NameText</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Exceptional</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Accessories 32 (1)</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>170</v>
+      </c>
+      <c r="G45" t="n">
+        <v>82</v>
+      </c>
+      <c r="H45" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I45" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>30043</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Equip30043NameText</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Exceptional</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Sword 02</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>180</v>
+      </c>
+      <c r="G46" t="n">
+        <v>227</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>30044</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Equip30044NameText</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Helmet</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Exceptional</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Helmet 32 (27)</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>180</v>
+      </c>
+      <c r="G47" t="n">
+        <v>65</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>30045</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Equip30045NameText</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Exceptional</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Torso 32 (27)</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>180</v>
+      </c>
+      <c r="G48" t="n">
+        <v>97</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>30046</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Equip30046NameText</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Exceptional</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Vambrace 32 (52)</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>180</v>
+      </c>
+      <c r="G49" t="n">
+        <v>78</v>
+      </c>
+      <c r="H49" t="n">
+        <v>8</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>30047</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Equip30047NameText</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Legs</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Exceptional</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Grieves 32 (9)</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>180</v>
+      </c>
+      <c r="G50" t="n">
+        <v>78</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>30048</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Equip30048NameText</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Exceptional</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Cloak 32 (16)</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>180</v>
+      </c>
+      <c r="G51" t="n">
+        <v>104</v>
+      </c>
+      <c r="H51" t="n">
+        <v>12</v>
+      </c>
+      <c r="I51" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>30049</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Equip30049NameText</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Icon_Sword_2</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>190</v>
+      </c>
+      <c r="G52" t="n">
+        <v>292</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>30050</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Equip30050NameText</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Helmet</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>helmet_01</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>190</v>
+      </c>
+      <c r="G53" t="n">
+        <v>83</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>30051</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Equip30051NameText</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Torso 32 (17)</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>190</v>
+      </c>
+      <c r="G54" t="n">
+        <v>125</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>30052</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Equip30052NameText</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Vambrace 32 (52)</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>190</v>
+      </c>
+      <c r="G55" t="n">
         <v>100</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H55" t="n">
+        <v>9</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>30053</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Equip30053NameText</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Legs</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Grieves 32 (9)</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>190</v>
+      </c>
+      <c r="G56" t="n">
+        <v>100</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>30054</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Equip30054NameText</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Accessories 32 (1)</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>190</v>
+      </c>
+      <c r="G57" t="n">
+        <v>133</v>
+      </c>
+      <c r="H57" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I57" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>30055</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Equip30055NameText</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Mystic</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Sword 32 (5)</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>200</v>
+      </c>
+      <c r="G58" t="n">
+        <v>365</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>30056</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Equip30056NameText</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Helmet</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Mystic</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Helmet 32 (27)</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>200</v>
+      </c>
+      <c r="G59" t="n">
+        <v>104</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>30057</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Equip30057NameText</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Mystic</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Torso 32 (27)</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>200</v>
+      </c>
+      <c r="G60" t="n">
+        <v>157</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>30058</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Equip30058NameText</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Gloves</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Mystic</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Vambrace 32 (52)</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>200</v>
+      </c>
+      <c r="G61" t="n">
+        <v>125</v>
+      </c>
+      <c r="H61" t="n">
         <v>10</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>30059</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Equip30059NameText</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Legs</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Mystic</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Grieves 32 (9)</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>200</v>
+      </c>
+      <c r="G62" t="n">
+        <v>125</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>30060</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Equip30060NameText</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Mystic</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Cloak 32 (16)</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>200</v>
+      </c>
+      <c r="G63" t="n">
+        <v>167</v>
+      </c>
+      <c r="H63" t="n">
+        <v>15</v>
+      </c>
+      <c r="I63" t="n">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/@Resources/Data/Excel/EquipmentData.xlsx
+++ b/Assets/@Resources/Data/Excel/EquipmentData.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sword01</t>
+          <t>Equip30001</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>helmet_01</t>
+          <t>Equip30002</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -652,7 +652,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Torso 32 (17)</t>
+          <t>Equip30003</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -689,7 +689,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vambrace 32 (52)</t>
+          <t>Equip30004</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grieves 32 (9)</t>
+          <t>Equip30005</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -763,7 +763,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Accessories 32 (1)</t>
+          <t>Equip30006</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sword03</t>
+          <t>Equip30007</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Helmet 32 (27)</t>
+          <t>Equip30008</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -874,7 +874,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torso 32 (27)</t>
+          <t>Equip30009</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vambrace 32 (52)</t>
+          <t>Equip30010</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -948,7 +948,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grieves 32 (9)</t>
+          <t>Equip30011</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -985,7 +985,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cloak 32 (16)</t>
+          <t>Equip30012</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sword 02</t>
+          <t>Equip30013</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>helmet_01</t>
+          <t>Equip30014</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Torso 32 (17)</t>
+          <t>Equip30015</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vambrace 32 (52)</t>
+          <t>Equip30016</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grieves 32 (9)</t>
+          <t>Equip30017</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Accessories 32 (1)</t>
+          <t>Equip30018</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Icon_Sword_2</t>
+          <t>Equip30019</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Helmet 32 (27)</t>
+          <t>Equip30020</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Torso 32 (27)</t>
+          <t>Equip30021</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vambrace 32 (52)</t>
+          <t>Equip30022</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Grieves 32 (9)</t>
+          <t>Equip30023</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cloak 32 (16)</t>
+          <t>Equip30024</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sword 32 (5)</t>
+          <t>Equip30025</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>helmet_01</t>
+          <t>Equip30026</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Torso 32 (17)</t>
+          <t>Equip30027</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vambrace 32 (52)</t>
+          <t>Equip30028</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Grieves 32 (9)</t>
+          <t>Equip30029</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Accessories 32 (1)</t>
+          <t>Equip30030</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sword01</t>
+          <t>Equip30031</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Helmet 32 (27)</t>
+          <t>Equip30032</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Torso 32 (27)</t>
+          <t>Equip30033</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vambrace 32 (52)</t>
+          <t>Equip30034</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grieves 32 (9)</t>
+          <t>Equip30035</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cloak 32 (16)</t>
+          <t>Equip30036</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sword03</t>
+          <t>Equip30037</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>helmet_01</t>
+          <t>Equip30038</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Torso 32 (17)</t>
+          <t>Equip30039</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vambrace 32 (52)</t>
+          <t>Equip30040</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Grieves 32 (9)</t>
+          <t>Equip30041</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Accessories 32 (1)</t>
+          <t>Equip30042</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sword 02</t>
+          <t>Equip30043</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Helmet 32 (27)</t>
+          <t>Equip30044</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Torso 32 (27)</t>
+          <t>Equip30045</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Vambrace 32 (52)</t>
+          <t>Equip30046</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Grieves 32 (9)</t>
+          <t>Equip30047</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cloak 32 (16)</t>
+          <t>Equip30048</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Icon_Sword_2</t>
+          <t>Equip30049</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>helmet_01</t>
+          <t>Equip30050</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Torso 32 (17)</t>
+          <t>Equip30051</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vambrace 32 (52)</t>
+          <t>Equip30052</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Grieves 32 (9)</t>
+          <t>Equip30053</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Accessories 32 (1)</t>
+          <t>Equip30054</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sword 32 (5)</t>
+          <t>Equip30055</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Helmet 32 (27)</t>
+          <t>Equip30056</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Torso 32 (27)</t>
+          <t>Equip30057</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vambrace 32 (52)</t>
+          <t>Equip30058</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Grieves 32 (9)</t>
+          <t>Equip30059</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cloak 32 (16)</t>
+          <t>Equip30060</t>
         </is>
       </c>
       <c r="F63" t="n">

--- a/Assets/@Resources/Data/Excel/EquipmentData.xlsx
+++ b/Assets/@Resources/Data/Excel/EquipmentData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2777,6 +2777,80 @@
         <v>84</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>30061</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Equip30061NameText</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Sword 32 (5)</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>110</v>
+      </c>
+      <c r="G64" t="n">
+        <v>18</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>30062</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Equip30062NameText</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Sword01</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>110</v>
+      </c>
+      <c r="G65" t="n">
+        <v>15</v>
+      </c>
+      <c r="H65" t="n">
+        <v>10</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
